--- a/ZGN.xlsx
+++ b/ZGN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5BA924-5179-47F7-BBFC-929500BA034C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9111B34B-6C99-4E8A-8052-AD55DB34D70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{E3433EC9-BF81-49D2-893F-3D58E7E5951B}"/>
   </bookViews>
@@ -267,7 +267,7 @@
     <t>H225</t>
   </si>
   <si>
-    <t>Q225</t>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -278,13 +278,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -479,44 +485,48 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -877,7 +887,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>9.6300000000000008</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -887,7 +897,7 @@
       <c r="J3" s="25">
         <v>253.02378999999999</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="29" t="s">
         <v>76</v>
       </c>
     </row>
@@ -900,7 +910,7 @@
       </c>
       <c r="J4" s="25">
         <f>+J2*J3</f>
-        <v>2436.6190977000001</v>
+        <v>2684.5824118999999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -911,10 +921,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="25">
-        <f>159.896+71.329</f>
-        <v>231.22499999999997</v>
-      </c>
-      <c r="K5" s="23" t="s">
+        <f>220.121+77.432</f>
+        <v>297.553</v>
+      </c>
+      <c r="K5" s="29" t="s">
         <v>76</v>
       </c>
     </row>
@@ -923,10 +933,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="25">
-        <f>174.235+174.418</f>
-        <v>348.65300000000002</v>
-      </c>
-      <c r="K6" s="23" t="s">
+        <f>162.123+84.066</f>
+        <v>246.18899999999999</v>
+      </c>
+      <c r="K6" s="29" t="s">
         <v>76</v>
       </c>
     </row>
@@ -951,7 +961,7 @@
       </c>
       <c r="J7" s="25">
         <f>+J4-J5+J6</f>
-        <v>2554.0470977000004</v>
+        <v>2633.2184118999999</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1090,7 +1100,9 @@
       <c r="R3" s="4">
         <v>281</v>
       </c>
-      <c r="S3" s="4"/>
+      <c r="S3" s="4">
+        <v>282</v>
+      </c>
     </row>
     <row r="4" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
@@ -1118,7 +1130,9 @@
       <c r="R4" s="4">
         <v>116</v>
       </c>
-      <c r="S4" s="4"/>
+      <c r="S4" s="4">
+        <v>123</v>
+      </c>
     </row>
     <row r="5" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -1146,7 +1160,9 @@
       <c r="R5" s="4">
         <v>64</v>
       </c>
-      <c r="S5" s="4"/>
+      <c r="S5" s="4">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:77" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
@@ -1174,7 +1190,10 @@
       <c r="R6" s="7">
         <v>461</v>
       </c>
-      <c r="S6" s="4"/>
+      <c r="S6" s="7">
+        <f>+SUM(S3:S5)</f>
+        <v>471</v>
+      </c>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
@@ -1230,7 +1249,9 @@
       <c r="R7" s="4">
         <v>118</v>
       </c>
-      <c r="S7" s="4"/>
+      <c r="S7" s="4">
+        <v>112</v>
+      </c>
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
@@ -1286,7 +1307,9 @@
       <c r="R8" s="4">
         <v>21</v>
       </c>
-      <c r="S8" s="4"/>
+      <c r="S8" s="4">
+        <v>18</v>
+      </c>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
@@ -1342,7 +1365,9 @@
       <c r="R9" s="4">
         <v>64</v>
       </c>
-      <c r="S9" s="4"/>
+      <c r="S9" s="4">
+        <v>65</v>
+      </c>
       <c r="T9" s="25"/>
       <c r="U9" s="25"/>
       <c r="V9" s="25"/>
@@ -1426,7 +1451,10 @@
       <c r="R10" s="4">
         <v>203</v>
       </c>
-      <c r="S10" s="4"/>
+      <c r="S10" s="4">
+        <f>+SUM(S7:S9)</f>
+        <v>195</v>
+      </c>
       <c r="T10" s="25"/>
       <c r="U10" s="25"/>
       <c r="V10" s="25"/>
@@ -1586,7 +1614,10 @@
       <c r="I12" s="25">
         <v>570.40899999999999</v>
       </c>
-      <c r="J12" s="25"/>
+      <c r="J12" s="25">
+        <f>+S12-I12</f>
+        <v>611.17400000000009</v>
+      </c>
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
@@ -1599,7 +1630,9 @@
       <c r="R12" s="25">
         <v>1163.722</v>
       </c>
-      <c r="S12" s="25"/>
+      <c r="S12" s="25">
+        <v>1181.5830000000001</v>
+      </c>
       <c r="T12" s="25"/>
       <c r="U12" s="25"/>
       <c r="V12" s="25"/>
@@ -1676,13 +1709,16 @@
         <v>166.721</v>
       </c>
       <c r="H13" s="25">
-        <f t="shared" ref="H13:H17" si="1">+R13-G13</f>
+        <f t="shared" ref="H13:H30" si="1">+R13-G13</f>
         <v>147.99099999999999</v>
       </c>
       <c r="I13" s="25">
         <v>129.154</v>
       </c>
-      <c r="J13" s="25"/>
+      <c r="J13" s="25">
+        <f>+S13-I13</f>
+        <v>139.315</v>
+      </c>
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
@@ -1695,7 +1731,9 @@
       <c r="R13" s="25">
         <v>314.71199999999999</v>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="25">
+        <v>268.46899999999999</v>
+      </c>
       <c r="T13" s="25"/>
       <c r="U13" s="25"/>
       <c r="V13" s="25"/>
@@ -1778,7 +1816,10 @@
       <c r="I14" s="25">
         <v>152.715</v>
       </c>
-      <c r="J14" s="25"/>
+      <c r="J14" s="25">
+        <f>+S14-I14</f>
+        <v>164.34099999999998</v>
+      </c>
       <c r="K14" s="25"/>
       <c r="L14" s="25"/>
       <c r="M14" s="25"/>
@@ -1791,7 +1832,9 @@
       <c r="R14" s="25">
         <v>314.51400000000001</v>
       </c>
-      <c r="S14" s="25"/>
+      <c r="S14" s="25">
+        <v>317.05599999999998</v>
+      </c>
       <c r="T14" s="25"/>
       <c r="U14" s="25"/>
       <c r="V14" s="25"/>
@@ -1874,7 +1917,10 @@
       <c r="I15" s="25">
         <v>67.061000000000007</v>
       </c>
-      <c r="J15" s="25"/>
+      <c r="J15" s="25">
+        <f>+S15-I15</f>
+        <v>67.168000000000006</v>
+      </c>
       <c r="K15" s="25"/>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
@@ -1887,7 +1933,9 @@
       <c r="R15" s="25">
         <v>138.15299999999999</v>
       </c>
-      <c r="S15" s="25"/>
+      <c r="S15" s="25">
+        <v>134.22900000000001</v>
+      </c>
       <c r="T15" s="25"/>
       <c r="U15" s="25"/>
       <c r="V15" s="25"/>
@@ -1970,7 +2018,10 @@
       <c r="I16" s="25">
         <v>8.3510000000000009</v>
       </c>
-      <c r="J16" s="25"/>
+      <c r="J16" s="25">
+        <f>+S16-I16</f>
+        <v>7.2589999999999986</v>
+      </c>
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
@@ -1983,7 +2034,9 @@
       <c r="R16" s="25">
         <v>15.545999999999999</v>
       </c>
-      <c r="S16" s="25"/>
+      <c r="S16" s="25">
+        <v>15.61</v>
+      </c>
       <c r="T16" s="25"/>
       <c r="U16" s="25"/>
       <c r="V16" s="25"/>
@@ -2066,7 +2119,10 @@
       <c r="I17" s="26">
         <v>927.69</v>
       </c>
-      <c r="J17" s="26"/>
+      <c r="J17" s="26">
+        <f>+S17-I17</f>
+        <v>989.25699999999983</v>
+      </c>
       <c r="K17" s="25"/>
       <c r="L17" s="26">
         <f t="shared" ref="L17:Q17" si="2">+SUM(L12:L16)</f>
@@ -2096,7 +2152,9 @@
         <f>+SUM(R12:R16)</f>
         <v>1946.6469999999999</v>
       </c>
-      <c r="S17" s="25"/>
+      <c r="S17" s="26">
+        <v>1916.9469999999999</v>
+      </c>
       <c r="T17" s="25"/>
       <c r="U17" s="25"/>
       <c r="V17" s="25"/>
@@ -2169,11 +2227,17 @@
       <c r="G18" s="25">
         <v>322.678</v>
       </c>
-      <c r="H18" s="25"/>
+      <c r="H18" s="25">
+        <f t="shared" si="1"/>
+        <v>327.40899999999999</v>
+      </c>
       <c r="I18" s="25">
         <v>301.65800000000002</v>
       </c>
-      <c r="J18" s="25"/>
+      <c r="J18" s="25">
+        <f>+S18-I18</f>
+        <v>321.25199999999995</v>
+      </c>
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
@@ -2181,8 +2245,12 @@
       <c r="O18" s="25"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
+      <c r="R18" s="28">
+        <v>650.08699999999999</v>
+      </c>
+      <c r="S18" s="25">
+        <v>622.91</v>
+      </c>
       <c r="T18" s="25"/>
       <c r="U18" s="25"/>
       <c r="V18" s="25"/>
@@ -2268,7 +2336,7 @@
       </c>
       <c r="H19" s="25">
         <f t="shared" ref="H19:J19" si="4">+H17-H18</f>
-        <v>986.53499999999997</v>
+        <v>659.12599999999998</v>
       </c>
       <c r="I19" s="25">
         <f t="shared" si="4"/>
@@ -2276,17 +2344,29 @@
       </c>
       <c r="J19" s="25">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>668.00499999999988</v>
       </c>
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
       <c r="N19" s="25"/>
       <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
+      <c r="P19" s="25">
+        <f t="shared" ref="P19:R19" si="5">+P17-P18</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="25">
+        <f t="shared" si="5"/>
+        <v>1904.5490000000002</v>
+      </c>
+      <c r="R19" s="25">
+        <f t="shared" si="5"/>
+        <v>1296.56</v>
+      </c>
+      <c r="S19" s="25">
+        <f>+S17-S18</f>
+        <v>1294.0369999999998</v>
+      </c>
       <c r="T19" s="25"/>
       <c r="U19" s="25"/>
       <c r="V19" s="25"/>
@@ -2359,11 +2439,17 @@
       <c r="G20" s="25">
         <v>497.61200000000002</v>
       </c>
-      <c r="H20" s="25"/>
+      <c r="H20" s="25">
+        <f t="shared" si="1"/>
+        <v>510.71199999999993</v>
+      </c>
       <c r="I20" s="25">
         <v>501.80399999999997</v>
       </c>
-      <c r="J20" s="25"/>
+      <c r="J20" s="25">
+        <f>+S20-I20</f>
+        <v>532.06700000000012</v>
+      </c>
       <c r="K20" s="25"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
@@ -2371,8 +2457,12 @@
       <c r="O20" s="25"/>
       <c r="P20" s="25"/>
       <c r="Q20" s="25"/>
-      <c r="R20" s="25"/>
-      <c r="S20" s="25"/>
+      <c r="R20" s="25">
+        <v>1008.324</v>
+      </c>
+      <c r="S20" s="25">
+        <v>1033.8710000000001</v>
+      </c>
       <c r="T20" s="25"/>
       <c r="U20" s="25"/>
       <c r="V20" s="25"/>
@@ -2445,11 +2535,17 @@
       <c r="G21" s="25">
         <v>66.751000000000005</v>
       </c>
-      <c r="H21" s="25"/>
+      <c r="H21" s="25">
+        <f t="shared" si="1"/>
+        <v>54.632999999999996</v>
+      </c>
       <c r="I21" s="25">
         <v>62.881999999999998</v>
       </c>
-      <c r="J21" s="25"/>
+      <c r="J21" s="25">
+        <f>+S21-I21</f>
+        <v>57.804000000000009</v>
+      </c>
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
@@ -2457,8 +2553,12 @@
       <c r="O21" s="25"/>
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="25"/>
+      <c r="R21" s="25">
+        <v>121.384</v>
+      </c>
+      <c r="S21" s="25">
+        <v>120.68600000000001</v>
+      </c>
       <c r="T21" s="25"/>
       <c r="U21" s="25"/>
       <c r="V21" s="25"/>
@@ -2523,19 +2623,19 @@
         <v>52</v>
       </c>
       <c r="C22" s="25">
-        <f t="shared" ref="C22:F22" si="5">+C19-C20-C21</f>
+        <f t="shared" ref="C22:F22" si="6">+C19-C20-C21</f>
         <v>0</v>
       </c>
       <c r="D22" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E22" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>116.50899999999993</v>
       </c>
       <c r="F22" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G22" s="25">
@@ -2543,16 +2643,16 @@
         <v>73.070999999999941</v>
       </c>
       <c r="H22" s="25">
-        <f t="shared" ref="H22:J22" si="6">+H19-H20-H21</f>
-        <v>986.53499999999997</v>
+        <f t="shared" ref="H22:J22" si="7">+H19-H20-H21</f>
+        <v>93.781000000000049</v>
       </c>
       <c r="I22" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>61.346000000000068</v>
       </c>
       <c r="J22" s="25">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>78.133999999999759</v>
       </c>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
@@ -2560,9 +2660,18 @@
       <c r="N22" s="25"/>
       <c r="O22" s="25"/>
       <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
+      <c r="Q22" s="25">
+        <f>+Q19-Q20-Q21</f>
+        <v>1904.5490000000002</v>
+      </c>
+      <c r="R22" s="25">
+        <f>+R19-R20-R21</f>
+        <v>166.85199999999998</v>
+      </c>
+      <c r="S22" s="25">
+        <f>+S19-S20-S21</f>
+        <v>139.47999999999971</v>
+      </c>
       <c r="T22" s="25"/>
       <c r="U22" s="25"/>
       <c r="V22" s="25"/>
@@ -2635,11 +2744,17 @@
       <c r="G23" s="25">
         <v>12.106</v>
       </c>
-      <c r="H23" s="25"/>
+      <c r="H23" s="25">
+        <f t="shared" si="1"/>
+        <v>13.921999999999999</v>
+      </c>
       <c r="I23" s="25">
         <v>21.207000000000001</v>
       </c>
-      <c r="J23" s="25"/>
+      <c r="J23" s="25">
+        <f>+S23-I23</f>
+        <v>20.302</v>
+      </c>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
       <c r="M23" s="25"/>
@@ -2647,8 +2762,12 @@
       <c r="O23" s="25"/>
       <c r="P23" s="25"/>
       <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
-      <c r="S23" s="25"/>
+      <c r="R23" s="25">
+        <v>26.027999999999999</v>
+      </c>
+      <c r="S23" s="25">
+        <v>41.509</v>
+      </c>
       <c r="T23" s="25"/>
       <c r="U23" s="25"/>
       <c r="V23" s="25"/>
@@ -2721,11 +2840,17 @@
       <c r="G24" s="25">
         <v>29.266999999999999</v>
       </c>
-      <c r="H24" s="25"/>
+      <c r="H24" s="25">
+        <f t="shared" si="1"/>
+        <v>22.727999999999998</v>
+      </c>
       <c r="I24" s="25">
         <v>25.408000000000001</v>
       </c>
-      <c r="J24" s="25"/>
+      <c r="J24" s="25">
+        <f>+S24-I24</f>
+        <v>25.062999999999995</v>
+      </c>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
       <c r="M24" s="25"/>
@@ -2733,8 +2858,12 @@
       <c r="O24" s="25"/>
       <c r="P24" s="25"/>
       <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
-      <c r="S24" s="25"/>
+      <c r="R24" s="25">
+        <v>51.994999999999997</v>
+      </c>
+      <c r="S24" s="25">
+        <v>50.470999999999997</v>
+      </c>
       <c r="T24" s="25"/>
       <c r="U24" s="25"/>
       <c r="V24" s="25"/>
@@ -2807,11 +2936,17 @@
       <c r="G25" s="25">
         <v>7.6840000000000002</v>
       </c>
-      <c r="H25" s="25"/>
+      <c r="H25" s="25">
+        <f t="shared" si="1"/>
+        <v>3.653999999999999</v>
+      </c>
       <c r="I25" s="25">
         <v>-10.214</v>
       </c>
-      <c r="J25" s="25"/>
+      <c r="J25" s="25">
+        <f>+S25-I25</f>
+        <v>1.2140000000000004</v>
+      </c>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
       <c r="M25" s="25"/>
@@ -2819,8 +2954,12 @@
       <c r="O25" s="25"/>
       <c r="P25" s="25"/>
       <c r="Q25" s="25"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="25"/>
+      <c r="R25" s="25">
+        <v>11.337999999999999</v>
+      </c>
+      <c r="S25" s="25">
+        <v>-9</v>
+      </c>
       <c r="T25" s="25"/>
       <c r="U25" s="25"/>
       <c r="V25" s="25"/>
@@ -2893,11 +3032,17 @@
       <c r="G26" s="25">
         <v>0.314</v>
       </c>
-      <c r="H26" s="25"/>
+      <c r="H26" s="25">
+        <f t="shared" si="1"/>
+        <v>0.74699999999999989</v>
+      </c>
       <c r="I26" s="25">
         <v>0.65900000000000003</v>
       </c>
-      <c r="J26" s="25"/>
+      <c r="J26" s="25">
+        <f>+S26-I26</f>
+        <v>-0.13500000000000001</v>
+      </c>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
       <c r="M26" s="25"/>
@@ -2905,8 +3050,12 @@
       <c r="O26" s="25"/>
       <c r="P26" s="25"/>
       <c r="Q26" s="25"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
+      <c r="R26" s="25">
+        <v>1.0609999999999999</v>
+      </c>
+      <c r="S26" s="25">
+        <v>0.52400000000000002</v>
+      </c>
       <c r="T26" s="25"/>
       <c r="U26" s="25"/>
       <c r="V26" s="25"/>
@@ -2971,19 +3120,19 @@
         <v>57</v>
       </c>
       <c r="C27" s="25">
-        <f t="shared" ref="C27:F27" si="7">+C22+C23-C24-C25+C26</f>
+        <f t="shared" ref="C27:F27" si="8">+C22+C23-C24-C25+C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E27" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>78.277999999999935</v>
       </c>
       <c r="F27" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G27" s="25">
@@ -2991,23 +3140,50 @@
         <v>48.539999999999942</v>
       </c>
       <c r="H27" s="25">
-        <f t="shared" ref="H27:I27" si="8">+H22+H23-H24-H25+H26</f>
-        <v>986.53499999999997</v>
+        <f t="shared" ref="H27:J27" si="9">+H22+H23-H24-H25+H26</f>
+        <v>82.068000000000055</v>
       </c>
       <c r="I27" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>68.018000000000072</v>
       </c>
-      <c r="J27" s="25"/>
+      <c r="J27" s="25">
+        <f t="shared" si="9"/>
+        <v>72.023999999999759</v>
+      </c>
       <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
+      <c r="L27" s="25">
+        <f t="shared" ref="L27:S27" si="10">+L22+L23-L24-L25+L26</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="25">
+        <f t="shared" si="10"/>
+        <v>1904.5490000000002</v>
+      </c>
+      <c r="R27" s="25">
+        <f t="shared" si="10"/>
+        <v>130.60799999999998</v>
+      </c>
+      <c r="S27" s="25">
+        <f t="shared" si="10"/>
+        <v>140.04199999999969</v>
+      </c>
       <c r="T27" s="25"/>
       <c r="U27" s="25"/>
       <c r="V27" s="25"/>
@@ -3080,11 +3256,17 @@
       <c r="G28" s="25">
         <v>17.218</v>
       </c>
-      <c r="H28" s="25"/>
+      <c r="H28" s="25">
+        <f t="shared" si="1"/>
+        <v>22.529</v>
+      </c>
       <c r="I28" s="25">
         <v>20.116</v>
       </c>
-      <c r="J28" s="25"/>
+      <c r="J28" s="25">
+        <f>+S28-I28</f>
+        <v>10.439</v>
+      </c>
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
       <c r="M28" s="25"/>
@@ -3092,8 +3274,12 @@
       <c r="O28" s="25"/>
       <c r="P28" s="25"/>
       <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="25"/>
+      <c r="R28" s="25">
+        <v>39.747</v>
+      </c>
+      <c r="S28" s="25">
+        <v>30.555</v>
+      </c>
       <c r="T28" s="25"/>
       <c r="U28" s="25"/>
       <c r="V28" s="25"/>
@@ -3158,19 +3344,19 @@
         <v>59</v>
       </c>
       <c r="C29" s="25">
-        <f t="shared" ref="C29:F29" si="9">+C27-C28</f>
+        <f t="shared" ref="C29:F29" si="11">+C27-C28</f>
         <v>0</v>
       </c>
       <c r="D29" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E29" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>52.115999999999936</v>
       </c>
       <c r="F29" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G29" s="25">
@@ -3178,23 +3364,35 @@
         <v>31.321999999999942</v>
       </c>
       <c r="H29" s="25">
-        <f t="shared" ref="H29:I29" si="10">+H27-H28</f>
-        <v>986.53499999999997</v>
+        <f t="shared" ref="H29:J29" si="12">+H27-H28</f>
+        <v>59.539000000000058</v>
       </c>
       <c r="I29" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>47.902000000000072</v>
       </c>
-      <c r="J29" s="25"/>
+      <c r="J29" s="25">
+        <f t="shared" si="12"/>
+        <v>61.584999999999759</v>
+      </c>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
       <c r="O29" s="25"/>
       <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="25"/>
-      <c r="S29" s="25"/>
+      <c r="Q29" s="25">
+        <f>+Q27-Q28</f>
+        <v>1904.5490000000002</v>
+      </c>
+      <c r="R29" s="25">
+        <f>+R27-R28</f>
+        <v>90.860999999999976</v>
+      </c>
+      <c r="S29" s="25">
+        <f>+S27-S28</f>
+        <v>109.48699999999968</v>
+      </c>
       <c r="T29" s="25"/>
       <c r="U29" s="25"/>
       <c r="V29" s="25"/>
@@ -3267,11 +3465,17 @@
       <c r="G30" s="25">
         <v>6.2469999999999999</v>
       </c>
-      <c r="H30" s="25"/>
+      <c r="H30" s="25">
+        <f t="shared" si="1"/>
+        <v>7.5310000000000006</v>
+      </c>
       <c r="I30" s="25">
         <v>4.819</v>
       </c>
-      <c r="J30" s="25"/>
+      <c r="J30" s="25">
+        <f>+S30-I30</f>
+        <v>6.0859999999999994</v>
+      </c>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
       <c r="M30" s="25"/>
@@ -3279,8 +3483,12 @@
       <c r="O30" s="25"/>
       <c r="P30" s="25"/>
       <c r="Q30" s="25"/>
-      <c r="R30" s="25"/>
-      <c r="S30" s="25"/>
+      <c r="R30" s="25">
+        <v>13.778</v>
+      </c>
+      <c r="S30" s="25">
+        <v>10.904999999999999</v>
+      </c>
       <c r="T30" s="25"/>
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
@@ -3345,19 +3553,19 @@
         <v>61</v>
       </c>
       <c r="C31" s="25">
-        <f t="shared" ref="C31:F31" si="11">+C29-C30</f>
+        <f t="shared" ref="C31:F31" si="13">+C29-C30</f>
         <v>0</v>
       </c>
       <c r="D31" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E31" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>45.966999999999935</v>
       </c>
       <c r="F31" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1001.4900000000002</v>
       </c>
       <c r="G31" s="25">
@@ -3365,23 +3573,41 @@
         <v>25.074999999999942</v>
       </c>
       <c r="H31" s="25">
-        <f t="shared" ref="H31:I31" si="12">+H29-H30</f>
-        <v>986.53499999999997</v>
+        <f t="shared" ref="H31:J31" si="14">+H29-H30</f>
+        <v>52.00800000000006</v>
       </c>
       <c r="I31" s="25">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>43.083000000000069</v>
       </c>
-      <c r="J31" s="25"/>
+      <c r="J31" s="25">
+        <f t="shared" si="14"/>
+        <v>55.498999999999761</v>
+      </c>
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="25"/>
-      <c r="S31" s="25"/>
+      <c r="O31" s="28">
+        <f t="shared" ref="O31:R31" si="15">+O29-O30</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="28">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="28">
+        <f t="shared" si="15"/>
+        <v>1904.5490000000002</v>
+      </c>
+      <c r="R31" s="28">
+        <f t="shared" si="15"/>
+        <v>77.08299999999997</v>
+      </c>
+      <c r="S31" s="28">
+        <f>+S29-S30</f>
+        <v>98.581999999999681</v>
+      </c>
       <c r="T31" s="25"/>
       <c r="U31" s="25"/>
       <c r="V31" s="25"/>
@@ -3495,34 +3721,37 @@
         <v>71</v>
       </c>
       <c r="C33" s="24" t="e">
-        <f t="shared" ref="C33:H33" si="13">+C31/C34</f>
+        <f t="shared" ref="C33:H33" si="16">+C31/C34</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="24" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="24" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F33" s="24" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.10004765739736834</v>
       </c>
-      <c r="H33" s="24" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+      <c r="H33" s="24">
+        <f t="shared" si="16"/>
+        <v>0.20750861678653443</v>
       </c>
       <c r="I33" s="24">
         <f>+I31/I34</f>
         <v>0.1702725265478004</v>
       </c>
-      <c r="J33" s="5"/>
+      <c r="J33" s="24">
+        <f>+J31/J34</f>
+        <v>0.21934301118483665</v>
+      </c>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
@@ -3530,8 +3759,14 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
+      <c r="R33" s="5">
+        <f>+R31/R34</f>
+        <v>0.30755627418390263</v>
+      </c>
+      <c r="S33" s="5">
+        <f>+S31/S34</f>
+        <v>0.38961553773263646</v>
+      </c>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
       <c r="V33" s="5"/>
@@ -3574,11 +3809,15 @@
       <c r="G34" s="5">
         <v>250.63055600000001</v>
       </c>
-      <c r="H34" s="5"/>
+      <c r="H34" s="5">
+        <v>250.63055600000001</v>
+      </c>
       <c r="I34" s="5">
         <v>253.02378999999999</v>
       </c>
-      <c r="J34" s="5"/>
+      <c r="J34" s="5">
+        <v>253.02378999999999</v>
+      </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
@@ -3586,8 +3825,12 @@
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
+      <c r="R34" s="5">
+        <v>250.63055600000001</v>
+      </c>
+      <c r="S34" s="5">
+        <v>253.02378999999999</v>
+      </c>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
@@ -3681,46 +3924,46 @@
         <v>4.5717959280941578E-2</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" ref="H36:J41" si="14">+H12/F12-1</f>
+        <f t="shared" ref="H36:J41" si="17">+H12/F12-1</f>
         <v>5.1890976676076894E-2</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>7.6704701033623035E-3</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="14"/>
-        <v>-1</v>
+        <f t="shared" si="17"/>
+        <v>2.2620073453748502E-2</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="9" t="e">
-        <f t="shared" ref="M36:N36" si="15">+M12/L12-1</f>
+        <f t="shared" ref="M36:N36" si="18">+M12/L12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N36" s="9" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O36" s="9" t="e">
-        <f t="shared" ref="O36:P36" si="16">+O12/N12-1</f>
+        <f t="shared" ref="O36:P36" si="19">+O12/N12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P36" s="9" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q36" s="9" t="e">
-        <f t="shared" ref="Q36:S40" si="17">+Q12/P12-1</f>
+        <f t="shared" ref="Q36:S40" si="20">+Q12/P12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>4.8879170718825193E-2</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" si="17"/>
-        <v>-1</v>
+        <f t="shared" si="20"/>
+        <v>1.5348167345809571E-2</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -3762,50 +4005,50 @@
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="9">
-        <f t="shared" ref="G37:G41" si="18">+G13/E13-1</f>
+        <f t="shared" ref="G37:G41" si="21">+G13/E13-1</f>
         <v>-0.19439384202057486</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-0.13687237182066869</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-0.22532854289501625</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="14"/>
-        <v>-1</v>
+        <f t="shared" si="17"/>
+        <v>-5.8625186666756646E-2</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="9" t="e">
-        <f t="shared" ref="M37:N37" si="19">+M13/L13-1</f>
+        <f t="shared" ref="M37:N37" si="22">+M13/L13-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N37" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O37" s="9" t="e">
-        <f t="shared" ref="O37:P37" si="20">+O13/N13-1</f>
+        <f t="shared" ref="O37:P37" si="23">+O13/N13-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P37" s="9" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q37" s="9" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q37" s="9" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="R37" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-0.16833064665310127</v>
       </c>
       <c r="S37" s="9">
-        <f t="shared" si="17"/>
-        <v>-1</v>
+        <f t="shared" si="20"/>
+        <v>-0.1469375174762958</v>
       </c>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
@@ -3847,50 +4090,50 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>1.3196594548152776</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-3.2037827374705619E-2</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2.8432316674860125E-2</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="14"/>
-        <v>-1</v>
+        <f t="shared" si="17"/>
+        <v>-1.0119201787725851E-2</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="9" t="e">
-        <f t="shared" ref="M38:N38" si="21">+M14/L14-1</f>
+        <f t="shared" ref="M38:N38" si="24">+M14/L14-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N38" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O38" s="9" t="e">
-        <f t="shared" ref="O38:P38" si="22">+O14/N14-1</f>
+        <f t="shared" ref="O38:P38" si="25">+O14/N14-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P38" s="9" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q38" s="9" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R38" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.33534014630770481</v>
       </c>
       <c r="S38" s="9">
-        <f t="shared" si="17"/>
-        <v>-1</v>
+        <f t="shared" si="20"/>
+        <v>8.0823111212855459E-3</v>
       </c>
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
@@ -3932,50 +4175,50 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-1.69148237354938E-2</v>
       </c>
       <c r="H39" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-0.14884359678620007</v>
       </c>
       <c r="I39" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-6.6470850270059501E-2</v>
       </c>
       <c r="J39" s="9">
-        <f t="shared" si="14"/>
-        <v>-1</v>
+        <f t="shared" si="17"/>
+        <v>1.2832305442043612E-2</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
       <c r="M39" s="9" t="e">
-        <f t="shared" ref="M39:N39" si="23">+M15/L15-1</f>
+        <f t="shared" ref="M39:N39" si="26">+M15/L15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N39" s="9" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O39" s="9" t="e">
-        <f t="shared" ref="O39:P39" si="24">+O15/N15-1</f>
+        <f t="shared" ref="O39:P39" si="27">+O15/N15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P39" s="9" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q39" s="9" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R39" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-8.4994635264196705E-2</v>
       </c>
       <c r="S39" s="9">
-        <f t="shared" si="17"/>
-        <v>-1</v>
+        <f t="shared" si="20"/>
+        <v>-2.8403292002345037E-2</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
@@ -4017,50 +4260,50 @@
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-0.60428200203366855</v>
       </c>
       <c r="H40" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-0.3128167994207095</v>
       </c>
       <c r="I40" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>0.19214846538187014</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="14"/>
-        <v>-1</v>
+        <f t="shared" si="17"/>
+        <v>-0.1500995199625339</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="9" t="e">
-        <f t="shared" ref="M40:N40" si="25">+M16/L16-1</f>
+        <f t="shared" ref="M40:N40" si="28">+M16/L16-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N40" s="9" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O40" s="9" t="e">
-        <f t="shared" ref="O40:P40" si="26">+O16/N16-1</f>
+        <f t="shared" ref="O40:P40" si="29">+O16/N16-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P40" s="9" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="9" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R40" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>-0.48405296870332881</v>
       </c>
       <c r="S40" s="9">
-        <f t="shared" si="17"/>
-        <v>-1</v>
+        <f t="shared" si="20"/>
+        <v>4.1168146146919327E-3</v>
       </c>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -4102,37 +4345,37 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>6.31774889569785E-2</v>
       </c>
       <c r="H41" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-1.4932750202198974E-2</v>
       </c>
       <c r="I41" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>-3.3768976952688767E-2</v>
       </c>
       <c r="J41" s="27">
-        <f t="shared" si="14"/>
-        <v>-1</v>
+        <f t="shared" si="17"/>
+        <v>2.7591519814298415E-3</v>
       </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
       <c r="M41" s="27" t="e">
-        <f t="shared" ref="M41:N41" si="27">+M17/L17-1</f>
+        <f t="shared" ref="M41:N41" si="30">+M17/L17-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N41" s="27" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O41" s="27" t="e">
-        <f t="shared" ref="O41:P41" si="28">+O17/N17-1</f>
+        <f t="shared" ref="O41:P41" si="31">+O17/N17-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P41" s="27" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q41" s="27" t="e">
@@ -4140,12 +4383,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R41" s="27">
-        <f t="shared" ref="R41:S41" si="29">+R17/Q17-1</f>
+        <f t="shared" ref="R41:S41" si="32">+R17/Q17-1</f>
         <v>2.2103920665732302E-2</v>
       </c>
       <c r="S41" s="27">
-        <f t="shared" si="29"/>
-        <v>-1</v>
+        <f t="shared" si="32"/>
+        <v>-1.525700345260339E-2</v>
       </c>
       <c r="T41" s="8"/>
       <c r="U41" s="8"/>
@@ -4183,19 +4426,19 @@
         <v>68</v>
       </c>
       <c r="C42" s="9" t="e">
-        <f t="shared" ref="C42:F42" si="30">+C19/C17</f>
+        <f t="shared" ref="C42:F42" si="33">+C19/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D42" s="9" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E42" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>0.64207432736952952</v>
       </c>
       <c r="F42" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G42" s="9">
@@ -4203,49 +4446,49 @@
         <v>0.66391629309913847</v>
       </c>
       <c r="H42" s="9">
-        <f t="shared" ref="H42:I42" si="31">+H19/H17</f>
-        <v>1</v>
+        <f t="shared" ref="H42:I42" si="34">+H19/H17</f>
+        <v>0.66812226631594418</v>
       </c>
       <c r="I42" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>0.67482887602539643</v>
       </c>
-      <c r="J42" s="9" t="e">
-        <f t="shared" ref="J42" si="32">+J19/J17</f>
-        <v>#DIV/0!</v>
+      <c r="J42" s="9">
+        <f t="shared" ref="J42" si="35">+J19/J17</f>
+        <v>0.67525931077566292</v>
       </c>
       <c r="K42" s="5"/>
       <c r="L42" s="9" t="e">
-        <f t="shared" ref="H42:S42" si="33">+L19/L17</f>
+        <f t="shared" ref="L42:S42" si="36">+L19/L17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M42" s="9" t="e">
-        <f t="shared" ref="M42:N42" si="34">+M19/M17</f>
+        <f t="shared" ref="M42:N42" si="37">+M19/M17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N42" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O42" s="9" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P42" s="9" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q42" s="9">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>1</v>
       </c>
       <c r="R42" s="9">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="36"/>
+        <v>0.66604782479822999</v>
+      </c>
+      <c r="S42" s="9">
+        <f t="shared" si="36"/>
+        <v>0.67505100558335718</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -4283,19 +4526,19 @@
         <v>69</v>
       </c>
       <c r="C43" s="9" t="e">
-        <f t="shared" ref="C43:F43" si="35">+C22/C17</f>
+        <f t="shared" ref="C43:F43" si="38">+C22/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D43" s="9" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E43" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.12901593362116975</v>
       </c>
       <c r="F43" s="9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="G43" s="9">
@@ -4303,49 +4546,49 @@
         <v>7.6106745879647317E-2</v>
       </c>
       <c r="H43" s="9">
-        <f t="shared" ref="H43:I43" si="36">+H22/H17</f>
-        <v>1</v>
+        <f t="shared" ref="H43:I43" si="39">+H22/H17</f>
+        <v>9.5060996315386739E-2</v>
       </c>
       <c r="I43" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>6.612769351830898E-2</v>
       </c>
-      <c r="J43" s="9" t="e">
-        <f t="shared" ref="J43" si="37">+J22/J17</f>
-        <v>#DIV/0!</v>
+      <c r="J43" s="9">
+        <f t="shared" ref="J43" si="40">+J22/J17</f>
+        <v>7.898250909520961E-2</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="9" t="e">
-        <f t="shared" ref="H43:S43" si="38">+L22/L17</f>
+        <f t="shared" ref="L43:S43" si="41">+L22/L17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M43" s="9" t="e">
-        <f t="shared" ref="M43:N43" si="39">+M22/M17</f>
+        <f t="shared" ref="M43:N43" si="42">+M22/M17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N43" s="9" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O43" s="9" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P43" s="9" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q43" s="9">
-        <f t="shared" si="38"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>1</v>
       </c>
       <c r="R43" s="9">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="9" t="e">
-        <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <f t="shared" si="41"/>
+        <v>8.5712509766793871E-2</v>
+      </c>
+      <c r="S43" s="9">
+        <f t="shared" si="41"/>
+        <v>7.2761531748138944E-2</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
@@ -4383,19 +4626,19 @@
         <v>70</v>
       </c>
       <c r="C44" s="9" t="e">
-        <f t="shared" ref="C44:F44" si="40">+C30/C29</f>
+        <f t="shared" ref="C44:F44" si="43">+C30/C29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D44" s="9" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E44" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0.11798679867986814</v>
       </c>
       <c r="F44" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="G44" s="9">
@@ -4403,49 +4646,49 @@
         <v>0.19944447991826866</v>
       </c>
       <c r="H44" s="9">
-        <f t="shared" ref="H44:I44" si="41">+H30/H29</f>
-        <v>0</v>
+        <f t="shared" ref="H44:I44" si="44">+H30/H29</f>
+        <v>0.1264885201296628</v>
       </c>
       <c r="I44" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>0.10060122750615826</v>
       </c>
-      <c r="J44" s="9" t="e">
-        <f t="shared" ref="J44" si="42">+J30/J29</f>
-        <v>#DIV/0!</v>
+      <c r="J44" s="9">
+        <f t="shared" ref="J44" si="45">+J30/J29</f>
+        <v>9.8822765283754541E-2</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="9" t="e">
-        <f t="shared" ref="H44:S44" si="43">+L30/L29</f>
+        <f t="shared" ref="L44:S44" si="46">+L30/L29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M44" s="9" t="e">
-        <f t="shared" ref="M44:N44" si="44">+M30/M29</f>
+        <f t="shared" ref="M44:N44" si="47">+M30/M29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N44" s="9" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O44" s="9" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P44" s="9" t="e">
-        <f t="shared" si="43"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q44" s="9" t="e">
-        <f t="shared" si="43"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R44" s="9" t="e">
-        <f t="shared" si="43"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S44" s="9" t="e">
-        <f t="shared" si="43"/>
-        <v>#DIV/0!</v>
+      <c r="Q44" s="9">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="9">
+        <f t="shared" si="46"/>
+        <v>0.15163821661659022</v>
+      </c>
+      <c r="S44" s="9">
+        <f t="shared" si="46"/>
+        <v>9.9600865856220661E-2</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
